--- a/terrestrial/Towards_SDS/Level2_SDS-aligned.xlsx
+++ b/terrestrial/Towards_SDS/Level2_SDS-aligned.xlsx
@@ -91,8 +91,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -464,1029 +467,1619 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.71" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="27.14" customWidth="1" min="2" max="2"/>
     <col width="13.86" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="13.86" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Local_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Full_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>term_localName/
+controlled_value_string</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>external url</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Level_1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>parent unit name</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>ISO_ter1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Northern Europe</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Middle Europe</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Southwestern Europe</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Southeastern Europe</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Eastern Europe</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Northern Africa</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Macaronesia</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>West Tropical Africa</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>West-Central Tropical Africa</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Northeast Tropical Africa</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>East Tropical Africa</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>South Tropical Africa</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Southern Africa</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Middle Atlantic Ocean</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Western Indian Ocean</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Siberia</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Asia-Temperate</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Russian Far East</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Asia-Temperate</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Middle Asia</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Asia-Temperate</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Caucasus</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Asia-Temperate</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Western Asia</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Asia-Temperate</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Arabian Peninsula</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Asia-Temperate</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Asia-Temperate</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Mongolia</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Asia-Temperate</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Eastern Asia</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Asia-Temperate</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Indian Subcontinent</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Asia-Tropical</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Indo-China</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Asia-Tropical</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Malesia</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Asia-Tropical</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>Papuasia</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Asia-Tropical</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Australasia</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Australasia</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>Southwestern Pacific</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>South-Central Pacific</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>Northwestern Pacific</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>North-Central Pacific</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>Subarctic America</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Northern America</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>Western Canada</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Northern America</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>Eastern Canada</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Northern America</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>Northwestern U.S.A.</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Northern America</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>North-Central U.S.A.</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Northern America</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>Northeastern U.S.A.</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Northern America</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>Southwestern U.S.A.</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="n"/>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Northern America</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>South-Central U.S.A.</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Northern America</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>Southeastern U.S.A.</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Northern America</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Northern America</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>Central America</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Southern America</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Caribbean</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Southern America</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>Northern South America</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="D48" s="3" t="n"/>
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="2" t="n"/>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Southern America</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>Western South America</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="D49" s="3" t="n"/>
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n"/>
-      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Southern America</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="D50" s="3" t="n"/>
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Southern America</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>Southern South America</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="D51" s="3" t="n"/>
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Southern America</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>Subantarctic Islands</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="D52" s="3" t="n"/>
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Antarctic</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>Antarctic Continent</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="D53" s="3" t="n"/>
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Antarctic</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/terrestrial/Towards_SDS/Level2_SDS-aligned.xlsx
+++ b/terrestrial/Towards_SDS/Level2_SDS-aligned.xlsx
@@ -549,7 +549,11 @@
         </is>
       </c>
       <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising DEN, FIN, FOR, GRB, ICE, IRE, NOR, SVA, and SWE.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -579,7 +583,11 @@
         </is>
       </c>
       <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising AUT, BGM, CZE, GER, HUN, NET, POL, and SWI.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -609,7 +617,11 @@
         </is>
       </c>
       <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising BAL, COR, FRA, POR, SAR, and SPA.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -639,7 +651,11 @@
         </is>
       </c>
       <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising ALB, BUL, GRC, ITA, KRI, NWB, ROM, SIC, and TUE.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -669,7 +685,11 @@
         </is>
       </c>
       <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising BLR, BLT, KRY, RUC, RUE, RUN, RUS, RUW, and UKR.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -699,7 +719,11 @@
         </is>
       </c>
       <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising ALG, EGY, LBY, MOR, TUN, and WSA.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -729,7 +753,11 @@
         </is>
       </c>
       <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising AZO, CNY, CVI, MDR, and SEL.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -759,7 +787,11 @@
         </is>
       </c>
       <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising BEN, BKN, GAM, GHA, GNB, GUI, IVO, LBR, MLI, MTN, NGA, NGR, SEN, SIE, and TOG.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -789,7 +821,11 @@
         </is>
       </c>
       <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising BUR, CAB, CAF, CMN, CON, EQG, GAB, GGI, RWA, and ZAI.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -819,7 +855,11 @@
         </is>
       </c>
       <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising CHA, DJI, ERI, ETH, SOC, SOM, and SUD.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -849,7 +889,11 @@
         </is>
       </c>
       <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising KEN, TAN, and UGA.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -879,7 +923,11 @@
         </is>
       </c>
       <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising ANG, MLW, MOZ, ZAM, and ZIM.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -909,7 +957,11 @@
         </is>
       </c>
       <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising BOT, CPP, CPV, ESW, LES, NAM, NAT, NPP, and OFS.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -939,7 +991,11 @@
         </is>
       </c>
       <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising ASC and STH.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -969,7 +1025,11 @@
         </is>
       </c>
       <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising ALD, CGS, COM, MAU, MCI, MDG, REU, ROD, and SEY.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -999,7 +1059,11 @@
         </is>
       </c>
       <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising ALT, BRY, CTA, IRK, KRA, TVA, WSB, and YAK.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1029,7 +1093,11 @@
         </is>
       </c>
       <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising AMU, KAM, KHA, KUR, MAG, PRM, and SAK.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1059,7 +1127,11 @@
         </is>
       </c>
       <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising KAZ, KGZ, TKM, TZK, and UZB.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1089,7 +1161,11 @@
         </is>
       </c>
       <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising NCS and TCS.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1119,7 +1195,11 @@
         </is>
       </c>
       <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising AFG, CYP, EAI, IRN, IRQ, LBS, PAL, SIN, and TUR.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1149,7 +1229,11 @@
         </is>
       </c>
       <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising GST, KUW, OMA, SAU, and YEM.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1179,7 +1263,11 @@
         </is>
       </c>
       <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising CHC, CHH, CHI, CHM, CHN, CHQ, CHS, CHT, and CHX.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1209,7 +1297,11 @@
         </is>
       </c>
       <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Mongolia</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1239,7 +1331,11 @@
         </is>
       </c>
       <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising JAP, KOR, KZN, NNS, OGA, and TAI.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1269,7 +1365,11 @@
         </is>
       </c>
       <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="n"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising ASS, BAN, EHM, IND, LDV, MDV, NEP, PAK, SRL, and WHM.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1299,7 +1399,11 @@
         </is>
       </c>
       <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising AND, CBD, LAO, MYA, NCB, SCS, THA, and VIE.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1329,7 +1433,11 @@
         </is>
       </c>
       <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="n"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising BOR, CKI, JAW, LSI, MLY, MOL, PHI, SUL, SUM, and XMS.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1359,7 +1467,11 @@
         </is>
       </c>
       <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising BIS, NWG, and SOL.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -1389,7 +1501,11 @@
         </is>
       </c>
       <c r="G30" s="3" t="n"/>
-      <c r="H30" s="3" t="n"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising NFK, NSW, NTA, QLD, SOA, TAS, VIC, and WAU.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1419,7 +1535,11 @@
         </is>
       </c>
       <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising ATP, CTM, KER, NZN, and NZS.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1449,7 +1569,11 @@
         </is>
       </c>
       <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="n"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising FIJ, GIL, HBI, NRU, NUE, NWC, PHX, SAM, SCZ, TOK, TON, TUV, VAN, and WAL.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1479,7 +1603,11 @@
         </is>
       </c>
       <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising COO, EAS, LIN, MRQ, PIT, SCI, TUA, and TUB.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -1509,7 +1637,11 @@
         </is>
       </c>
       <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising CRL, MCS, MRN, MRS, and WAK.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -1539,7 +1671,11 @@
         </is>
       </c>
       <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising HAW-HI, HAW-JI, and HAW-MI.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -1569,7 +1705,11 @@
         </is>
       </c>
       <c r="G36" s="3" t="n"/>
-      <c r="H36" s="3" t="n"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising ALU, ASK, GNL, NUN, NWT, and YUK.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1599,7 +1739,11 @@
         </is>
       </c>
       <c r="G37" s="3" t="n"/>
-      <c r="H37" s="3" t="n"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising ABT, BRC, MAN, and SAS.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1629,7 +1773,11 @@
         </is>
       </c>
       <c r="G38" s="3" t="n"/>
-      <c r="H38" s="3" t="n"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising LAB, NBR, NFL, NSC, ONT, PEI, and QUE.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1659,7 +1807,11 @@
         </is>
       </c>
       <c r="G39" s="3" t="n"/>
-      <c r="H39" s="3" t="n"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising COL, IDA, MNT, ORE, WAS, and WYO.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1689,7 +1841,11 @@
         </is>
       </c>
       <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising ILL, IOW, KAN, MIN, MSO, NDA, NEB, OKL, SDA, and WIS.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1719,7 +1875,11 @@
         </is>
       </c>
       <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising CNT, INI, MAI, MAS, MIC, NWH, NWJ, NWY, OHI, PEN, RHO, VER, and WVA.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -1749,7 +1909,11 @@
         </is>
       </c>
       <c r="G42" s="3" t="n"/>
-      <c r="H42" s="3" t="n"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising ARI, CAL, NEV, and UTA.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -1779,7 +1943,11 @@
         </is>
       </c>
       <c r="G43" s="3" t="n"/>
-      <c r="H43" s="3" t="n"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising NWM and TEX.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -1809,7 +1977,11 @@
         </is>
       </c>
       <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="n"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising ALA, ARK, DEL, FLA, GEO, KTY, LOU, MRY, MSI, NCA, SCA, TEN, VRG, and WDC.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1839,7 +2011,11 @@
         </is>
       </c>
       <c r="G45" s="3" t="n"/>
-      <c r="H45" s="3" t="n"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising MXC, MXE, MXG, MXI, MXN, MXS, and MXT.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -1869,7 +2045,11 @@
         </is>
       </c>
       <c r="G46" s="3" t="n"/>
-      <c r="H46" s="3" t="n"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising BLZ, COS, CPI, ELS, GUA, HON, NIC, and PAN.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1899,7 +2079,11 @@
         </is>
       </c>
       <c r="G47" s="3" t="n"/>
-      <c r="H47" s="3" t="n"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising ARU, BAH, BER, CAY, CUB, DOM, HAI, JAM, LEE, NLA, PUE, SWC, TCI, TRT, VNA, and WIN.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -1929,7 +2113,11 @@
         </is>
       </c>
       <c r="G48" s="3" t="n"/>
-      <c r="H48" s="3" t="n"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising FRG, GUY, SUR, and VEN.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -1959,7 +2147,11 @@
         </is>
       </c>
       <c r="G49" s="3" t="n"/>
-      <c r="H49" s="3" t="n"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising BOL, CLM, ECU, GAL, and PER.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -1989,7 +2181,11 @@
         </is>
       </c>
       <c r="G50" s="3" t="n"/>
-      <c r="H50" s="3" t="n"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising BZC, BZE, BZL, BZN, and BZS.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -2019,7 +2215,11 @@
         </is>
       </c>
       <c r="G51" s="3" t="n"/>
-      <c r="H51" s="3" t="n"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising AGE, AGS, AGW, CLC, CLN, CLS, DSV, JNF, PAR, and URU.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -2049,7 +2249,11 @@
         </is>
       </c>
       <c r="G52" s="3" t="n"/>
-      <c r="H52" s="3" t="n"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>The territory comprising ASP, BOU, CRZ, FAL, HMD, KEG, MAQ, MPE, SGE, SSA, and TDC.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -2079,7 +2283,11 @@
         </is>
       </c>
       <c r="G53" s="3" t="n"/>
-      <c r="H53" s="3" t="n"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Antarctica</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
